--- a/data/Mar/20-03-2026/NGAY 20-03.xlsx
+++ b/data/Mar/20-03-2026/NGAY 20-03.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\Freelance\TextInputter\data\Mar\20-03-2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13EF7322-EE02-4C75-979B-0E2E89914769}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{545ABFC9-3CAA-4519-8017-4FFD94EAAA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{6B6C9D35-2D77-4262-A067-18EED5C7F01A}"/>
   </bookViews>
@@ -534,13 +534,13 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1027,45 +1027,45 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:17" s="17" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="17" t="s">
+    <row r="5" spans="1:17" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="D5" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E5" s="17" t="s">
+      <c r="E5" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="13">
         <v>7</v>
       </c>
-      <c r="G5" s="18">
+      <c r="G5" s="13">
         <v>0</v>
       </c>
-      <c r="H5" s="18">
+      <c r="H5" s="13">
         <v>30</v>
       </c>
-      <c r="I5" s="18">
+      <c r="I5" s="13">
         <f>G5-H5</f>
         <v>-30</v>
       </c>
       <c r="J5" t="s">
         <v>58</v>
       </c>
-      <c r="K5" s="17" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" s="17" t="s">
+      <c r="K5" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="12" t="s">
         <v>59</v>
       </c>
-      <c r="M5" s="17" t="s">
+      <c r="M5" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="Q5" s="18">
+      <c r="Q5" s="13">
         <v>1</v>
       </c>
     </row>
@@ -1998,10 +1998,10 @@
       <c r="A31" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C31" s="14" t="s">
+      <c r="C31" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="D31" s="14"/>
+      <c r="D31" s="16"/>
       <c r="E31" s="4" t="s">
         <v>36</v>
       </c>
@@ -2029,11 +2029,11 @@
       <c r="B32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C32" s="15">
+      <c r="C32" s="17">
         <f>SUMIFS(I$3:I$27,B$3:B$27,A$31,L$3:L$27,A$32)</f>
         <v>8730</v>
       </c>
-      <c r="D32" s="15"/>
+      <c r="D32" s="17"/>
       <c r="E32" s="3">
         <f>SUMIFS(Q$3:Q$27,B$3:B$27,A$31,L$3:L$27,A$32)</f>
         <v>24</v>
@@ -2068,10 +2068,10 @@
       <c r="B33" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C33" s="16">
+      <c r="C33" s="18">
         <v>0</v>
       </c>
-      <c r="D33" s="16"/>
+      <c r="D33" s="18"/>
       <c r="K33" t="s">
         <v>43</v>
       </c>
@@ -2095,11 +2095,11 @@
       <c r="B34" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C34" s="16">
+      <c r="C34" s="18">
         <f>-SUMIFS(I$3:I$27,B$3:B$27,A$31,P$3:P$27,"xx",N$3:N$27,"x")</f>
         <v>-1450</v>
       </c>
-      <c r="D34" s="16"/>
+      <c r="D34" s="18"/>
       <c r="E34" s="2">
         <f>SUMIFS(Q$3:Q$27,B$3:B$27,A$31,P$3:P$27,"xx",N$3:N$27,"x")</f>
         <v>1</v>
@@ -2119,11 +2119,11 @@
       <c r="B35" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="14">
+      <c r="C35" s="16">
         <f>SUBTOTAL(9,C32:C34)</f>
         <v>7280</v>
       </c>
-      <c r="D35" s="14"/>
+      <c r="D35" s="16"/>
       <c r="E35">
         <f>E32</f>
         <v>24</v>
@@ -2143,8 +2143,8 @@
       <c r="B36" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C36" s="12"/>
-      <c r="D36" s="12"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
       <c r="K36" s="2" t="s">
         <v>49</v>
       </c>
@@ -2160,8 +2160,8 @@
       <c r="B37" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="C37" s="12"/>
-      <c r="D37" s="12"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
       <c r="L37" s="9">
         <f>SUBTOTAL(9,L32:L36)</f>
         <v>2454</v>
@@ -2182,11 +2182,11 @@
       <c r="B39" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="13">
+      <c r="C39" s="15">
         <f>C35+C36+C37</f>
         <v>7280</v>
       </c>
-      <c r="D39" s="13"/>
+      <c r="D39" s="15"/>
       <c r="E39" s="1" t="s">
         <v>54</v>
       </c>
